--- a/TestFiles-prod-sanity/Chargeback/Chargeback+AG1+AetnaACA[NB].xlsx
+++ b/TestFiles-prod-sanity/Chargeback/Chargeback+AG1+AetnaACA[NB].xlsx
@@ -91,7 +91,7 @@
     <t>Integrity Health, LLC</t>
   </si>
   <si>
-    <t>AETNA-TEST-CBK-028</t>
+    <t>AETNA-TEST-CBK-034</t>
   </si>
   <si>
     <t>ROBERTS, PIPPIN</t>
